--- a/Training/Day3_Calibration/ScenarioPathDefinition.xlsx
+++ b/Training/Day3_Calibration/ScenarioPathDefinition.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="212">
   <si>
     <t>Baseline Path Definition Template</t>
   </si>
@@ -479,6 +479,114 @@
   </si>
   <si>
     <t>exo_PVEff_1_2</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_2_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+  </si>
+  <si>
+    <t>exo_targetIY_3_1</t>
+  </si>
+  <si>
+    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
   </si>
   <si>
     <t>exo_targetIY_2_1</t>
@@ -4125,10 +4233,10 @@
         <v>30</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="9">
@@ -4215,10 +4323,10 @@
         <v>31</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="9">

--- a/Training/Day3_Calibration/ScenarioPathDefinition.xlsx
+++ b/Training/Day3_Calibration/ScenarioPathDefinition.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schul\Documents\GitHub\DGE-METRIC\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3EAE3-2D70-4869-880C-20B243CE7DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82089CF5-50CD-4A37-AB6F-A765CD6DB62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="NZ" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="NZ" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="160">
   <si>
     <t>Baseline Path Definition Template</t>
   </si>
@@ -475,10 +476,10 @@
     <t>FDI interest rate - Renewables</t>
   </si>
   <si>
-    <t>exo_PV_1_2</t>
-  </si>
-  <si>
-    <t>exo_PVEff_1_2</t>
+    <t>No ETS covered emissions by agriculture</t>
+  </si>
+  <si>
+    <t>exo_PVEff_1</t>
   </si>
   <si>
     <t>exo_targetIY_2_1</t>
@@ -493,6 +494,12 @@
     <t>direct (share of GDP from PDP8 investment + maintenance)</t>
   </si>
   <si>
+    <t>exo_E_NOETS_1_1</t>
+  </si>
+  <si>
+    <t>log(index/index(1))</t>
+  </si>
+  <si>
     <t>exo_targetIY_2_1</t>
   </si>
   <si>
@@ -505,172 +512,10 @@
     <t>direct (share of GDP from PDP8 investment + maintenance)</t>
   </si>
   <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_2_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
-  </si>
-  <si>
-    <t>exo_targetIY_3_1</t>
-  </si>
-  <si>
-    <t>direct (share of GDP from PDP8 investment + maintenance)</t>
+    <t>exo_E_NOETS_1_1</t>
+  </si>
+  <si>
+    <t>log(index/index(1))</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD100"/>
+  <dimension ref="A1:AE100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.6640625" customWidth="true"/>
@@ -3552,6 +3397,96 @@
         <v>1E-3</v>
       </c>
     </row>
+    <row r="48" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="11">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11">
+        <v>1</v>
+      </c>
+      <c r="G48" s="11">
+        <v>1</v>
+      </c>
+      <c r="H48" s="11">
+        <v>1</v>
+      </c>
+      <c r="I48" s="11">
+        <v>1</v>
+      </c>
+      <c r="J48" s="11">
+        <v>1</v>
+      </c>
+      <c r="K48" s="11">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="L48" s="11">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="M48" s="11">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="N48" s="11">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="O48" s="11">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="P48" s="11">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Q48" s="11">
+        <v>0.90277777777777779</v>
+      </c>
+      <c r="R48" s="11">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="S48" s="11">
+        <v>0.875</v>
+      </c>
+      <c r="T48" s="11">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="U48" s="11">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="V48" s="11">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W48" s="11">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="X48" s="11">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="Y48" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="Z48" s="11">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AA48" s="11">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="AB48" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="AC48" s="11">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="AD48" s="11">
+        <v>0.72222222222222221</v>
+      </c>
+    </row>
     <row r="50" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>23</v>
@@ -4233,10 +4168,10 @@
         <v>30</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="9">
@@ -4323,10 +4258,10 @@
         <v>31</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="9">
@@ -6933,90 +6868,92 @@
         <v>60</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>103</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="9">
-        <v>1</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="F94" s="9">
-        <v>1.067571</v>
+        <v>3.1663720000000002E-3</v>
       </c>
       <c r="G94" s="9">
-        <v>1.1397600000000001</v>
+        <v>5.1978459999999999E-3</v>
       </c>
       <c r="H94" s="9">
-        <v>1.216888</v>
+        <v>1.3292877E-2</v>
       </c>
       <c r="I94" s="9">
-        <v>1.299296</v>
+        <v>2.5726505E-2</v>
       </c>
       <c r="J94" s="9">
-        <v>1.387348</v>
+        <v>1.0399210000000001E-2</v>
       </c>
       <c r="K94" s="9">
-        <v>1.4814369999999999</v>
+        <v>1.0975494000000001E-2</v>
       </c>
       <c r="L94" s="9">
-        <v>1.5819810000000001</v>
+        <v>1.1558150999999999E-2</v>
       </c>
       <c r="M94" s="9">
-        <v>1.689427</v>
+        <v>1.2147181999999999E-2</v>
       </c>
       <c r="N94" s="9">
-        <v>1.8042549999999999</v>
+        <v>1.2742587999999999E-2</v>
       </c>
       <c r="O94" s="9">
-        <v>1.9269769999999999</v>
+        <v>1.8810360000000002E-2</v>
       </c>
       <c r="P94" s="9">
-        <v>2.0581420000000001</v>
+        <v>2.0035783000000001E-2</v>
       </c>
       <c r="Q94" s="9">
-        <v>2.1983380000000001</v>
+        <v>2.1274648E-2</v>
       </c>
       <c r="R94" s="9">
-        <v>2.3481920000000001</v>
+        <v>2.2526952999999999E-2</v>
       </c>
       <c r="S94" s="9">
-        <v>2.5083769999999999</v>
+        <v>2.37927E-2</v>
       </c>
       <c r="T94" s="9">
-        <v>2.6796139999999999</v>
+        <v>2.6232307999999999E-2</v>
       </c>
       <c r="U94" s="9">
-        <v>2.862673</v>
+        <v>2.7655513E-2</v>
       </c>
       <c r="V94" s="9">
-        <v>3.0583800000000001</v>
+        <v>2.9093612000000001E-2</v>
       </c>
       <c r="W94" s="9">
-        <v>3.267617</v>
+        <v>3.0546605000000001E-2</v>
       </c>
       <c r="X94" s="9">
-        <v>3.49133</v>
+        <v>3.2014492999999998E-2</v>
       </c>
       <c r="Y94" s="9">
-        <v>3.730531</v>
+        <v>2.4751406E-2</v>
       </c>
       <c r="Z94" s="9">
-        <v>3.9863029999999999</v>
+        <v>2.5268286000000001E-2</v>
       </c>
       <c r="AA94" s="9">
-        <v>4.2598079999999996</v>
+        <v>2.5789439000000001E-2</v>
       </c>
       <c r="AB94" s="9">
-        <v>4.5522869999999998</v>
+        <v>2.6314865999999999E-2</v>
       </c>
       <c r="AC94" s="9">
-        <v>4.8650700000000002</v>
+        <v>2.6844567E-2</v>
       </c>
       <c r="AD94" s="9">
-        <v>5.1995820000000004</v>
-      </c>
+        <f>AC94</f>
+        <v>2.6844567E-2</v>
+      </c>
+      <c r="AE94" s="6"/>
     </row>
     <row r="95" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
@@ -7475,8 +7412,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47456956-2FBE-4208-AD35-651AA7A3EED7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43475D6D-90C7-4C54-90FC-AAB5B9C359F2}">
-  <dimension ref="D10:E35"/>
+  <dimension ref="D10:H61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="10" x14ac:dyDescent="0.3">
@@ -7685,6 +7631,136 @@
       </c>
       <c r="E35">
         <v>1.2370820668693012</v>
+      </c>
+    </row>
+    <row r="36" x14ac:dyDescent="0.3">
+      <c r="H36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" x14ac:dyDescent="0.3">
+      <c r="H37">
+        <v>1.2999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="38" x14ac:dyDescent="0.3">
+      <c r="H38">
+        <v>3.1663720000000002E-3</v>
+      </c>
+    </row>
+    <row r="39" x14ac:dyDescent="0.3">
+      <c r="H39">
+        <v>5.1978459999999999E-3</v>
+      </c>
+    </row>
+    <row r="40" x14ac:dyDescent="0.3">
+      <c r="H40">
+        <v>1.3292877E-2</v>
+      </c>
+    </row>
+    <row r="41" x14ac:dyDescent="0.3">
+      <c r="H41">
+        <v>2.5726505E-2</v>
+      </c>
+    </row>
+    <row r="42" x14ac:dyDescent="0.3">
+      <c r="H42">
+        <v>1.0399210000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" x14ac:dyDescent="0.3">
+      <c r="H43">
+        <v>1.0975494000000001E-2</v>
+      </c>
+    </row>
+    <row r="44" x14ac:dyDescent="0.3">
+      <c r="H44">
+        <v>1.1558150999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" x14ac:dyDescent="0.3">
+      <c r="H45">
+        <v>1.2147181999999999E-2</v>
+      </c>
+    </row>
+    <row r="46" x14ac:dyDescent="0.3">
+      <c r="H46">
+        <v>1.2742587999999999E-2</v>
+      </c>
+    </row>
+    <row r="47" x14ac:dyDescent="0.3">
+      <c r="H47">
+        <v>1.8810360000000002E-2</v>
+      </c>
+    </row>
+    <row r="48" x14ac:dyDescent="0.3">
+      <c r="H48">
+        <v>2.0035783000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" x14ac:dyDescent="0.3">
+      <c r="H49">
+        <v>2.1274648E-2</v>
+      </c>
+    </row>
+    <row r="50" x14ac:dyDescent="0.3">
+      <c r="H50">
+        <v>2.2526952999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" x14ac:dyDescent="0.3">
+      <c r="H51">
+        <v>2.37927E-2</v>
+      </c>
+    </row>
+    <row r="52" x14ac:dyDescent="0.3">
+      <c r="H52">
+        <v>2.6232307999999999E-2</v>
+      </c>
+    </row>
+    <row r="53" x14ac:dyDescent="0.3">
+      <c r="H53">
+        <v>2.7655513E-2</v>
+      </c>
+    </row>
+    <row r="54" x14ac:dyDescent="0.3">
+      <c r="H54">
+        <v>2.9093612000000001E-2</v>
+      </c>
+    </row>
+    <row r="55" x14ac:dyDescent="0.3">
+      <c r="H55">
+        <v>3.0546605000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>3.2014492999999998E-2</v>
+      </c>
+    </row>
+    <row r="57" x14ac:dyDescent="0.3">
+      <c r="H57">
+        <v>2.4751406E-2</v>
+      </c>
+    </row>
+    <row r="58" x14ac:dyDescent="0.3">
+      <c r="H58">
+        <v>2.5268286000000001E-2</v>
+      </c>
+    </row>
+    <row r="59" x14ac:dyDescent="0.3">
+      <c r="H59">
+        <v>2.5789439000000001E-2</v>
+      </c>
+    </row>
+    <row r="60" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <v>2.6314865999999999E-2</v>
+      </c>
+    </row>
+    <row r="61" x14ac:dyDescent="0.3">
+      <c r="H61">
+        <v>2.6844567E-2</v>
       </c>
     </row>
   </sheetData>
@@ -7692,7 +7768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
